--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.59629</v>
+        <v>17.04205</v>
       </c>
       <c r="D2" t="n">
-        <v>16.15455</v>
+        <v>16.50503</v>
       </c>
       <c r="E2" t="n">
-        <v>16.49188</v>
+        <v>16.69626</v>
       </c>
       <c r="F2" t="n">
-        <v>42.49215</v>
+        <v>42.37394</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05101</v>
+        <v>0.05031</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81825</v>
+        <v>1.77844</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.47565</v>
+        <v>16.81736</v>
       </c>
       <c r="D3" t="n">
-        <v>16.61286</v>
+        <v>16.14626</v>
       </c>
       <c r="E3" t="n">
-        <v>16.91463</v>
+        <v>16.49005</v>
       </c>
       <c r="F3" t="n">
-        <v>41.18908</v>
+        <v>42.1127</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05023</v>
+        <v>0.05041</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80853</v>
+        <v>1.79562</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.51745</v>
+        <v>16.70958</v>
       </c>
       <c r="D4" t="n">
-        <v>16.55271</v>
+        <v>16.39859</v>
       </c>
       <c r="E4" t="n">
-        <v>16.43909</v>
+        <v>16.58964</v>
       </c>
       <c r="F4" t="n">
-        <v>42.49905</v>
+        <v>42.32603</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0491</v>
+        <v>0.05001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80525</v>
+        <v>1.80396</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.56891</v>
+        <v>16.64416</v>
       </c>
       <c r="D6" t="n">
-        <v>15.47784</v>
+        <v>16.26351</v>
       </c>
       <c r="E6" t="n">
-        <v>16.05437</v>
+        <v>16.3752</v>
       </c>
       <c r="F6" t="n">
-        <v>21.81231</v>
+        <v>21.25981</v>
       </c>
       <c r="G6" t="n">
-        <v>33.88266</v>
+        <v>33.57602</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.77566</v>
+        <v>16.44296</v>
       </c>
       <c r="D7" t="n">
-        <v>15.43144</v>
+        <v>15.66536</v>
       </c>
       <c r="E7" t="n">
-        <v>16.17772</v>
+        <v>16.18671</v>
       </c>
       <c r="F7" t="n">
-        <v>21.83453</v>
+        <v>21.61899</v>
       </c>
       <c r="G7" t="n">
-        <v>34.59747</v>
+        <v>33.6344</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.49033</v>
+        <v>16.73354</v>
       </c>
       <c r="D8" t="n">
-        <v>15.55153</v>
+        <v>16.1513</v>
       </c>
       <c r="E8" t="n">
-        <v>15.85822</v>
+        <v>16.1566</v>
       </c>
       <c r="F8" t="n">
-        <v>21.27105</v>
+        <v>21.90382</v>
       </c>
       <c r="G8" t="n">
-        <v>34.52475</v>
+        <v>34.03281</v>
       </c>
     </row>
   </sheetData>
